--- a/ig/improve-doc/StructureDefinition-ans-shareable-codesystem.xlsx
+++ b/ig/improve-doc/StructureDefinition-ans-shareable-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T15:55:45+00:00</t>
+    <t>2024-11-26T12:51:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/StructureDefinition-ans-shareable-codesystem.xlsx
+++ b/ig/improve-doc/StructureDefinition-ans-shareable-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T12:51:17+00:00</t>
+    <t>2024-11-26T14:12:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/StructureDefinition-ans-shareable-codesystem.xlsx
+++ b/ig/improve-doc/StructureDefinition-ans-shareable-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T14:12:54+00:00</t>
+    <t>2024-12-02T10:46:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/StructureDefinition-ans-shareable-codesystem.xlsx
+++ b/ig/improve-doc/StructureDefinition-ans-shareable-codesystem.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3264" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3264" uniqueCount="497">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-02T10:46:43+00:00</t>
+    <t>2024-12-02T16:50:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -817,7 +817,7 @@
     <t>CodeSystem.url</t>
   </si>
   <si>
-    <t>L'ANS est autorité sur les URLs de type https://mos.esante.gouv.fr/fhir/CodeSystem/* et https://smt.esante.gouv.fr/fhir/CodeSystem/*</t>
+    <t>L'URL doit être de type https://smt.esante.gouv.fr/fhir/CodeSystem/*</t>
   </si>
   <si>
     <t>An absolute URI that is used to identify this code system when it is referenced in a specification, model, design or an instance; also called its canonical identifier. This SHOULD be globally unique and SHOULD be a literal address at which at which an authoritative instance of this code system is (or will be) published. This URL can be the target of a canonical reference. It SHALL remain the same when the code system is stored on different servers. This is used in [Coding](http://hl7.org/fhir/datatypes.html#Coding).system.</t>
@@ -829,6 +829,10 @@
   </si>
   <si>
     <t>Allows the code system to be referenced by a single globally unique identifier.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ans-cs-url-regex:url matches smt regex {$this.matches('https:\/\/smt.esante.gouv.fr\/fhir\/CodeSystem\/[a-z0-9]+(?:-[a-z0-9]+)*')}</t>
   </si>
   <si>
     <t>Definition.url</t>
@@ -5432,16 +5436,16 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>260</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>75</v>
@@ -5449,10 +5453,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5475,19 +5479,19 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>75</v>
@@ -5536,7 +5540,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5554,21 +5558,21 @@
         <v>75</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5594,13 +5598,13 @@
         <v>99</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5650,7 +5654,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5668,10 +5672,10 @@
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>75</v>
@@ -5679,10 +5683,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5708,16 +5712,16 @@
         <v>99</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5766,7 +5770,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5775,7 +5779,7 @@
         <v>76</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>97</v>
@@ -5795,10 +5799,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5824,13 +5828,13 @@
         <v>99</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5880,7 +5884,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5898,7 +5902,7 @@
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>75</v>
@@ -5909,10 +5913,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5938,13 +5942,13 @@
         <v>167</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5973,10 +5977,10 @@
         <v>151</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -5994,7 +5998,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6012,10 +6016,10 @@
         <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>75</v>
@@ -6023,10 +6027,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6049,19 +6053,19 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -6110,7 +6114,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6128,10 +6132,10 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>75</v>
@@ -6139,14 +6143,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6168,13 +6172,13 @@
         <v>225</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6224,7 +6228,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6242,10 +6246,10 @@
         <v>75</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>75</v>
@@ -6253,14 +6257,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6282,16 +6286,16 @@
         <v>99</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -6340,7 +6344,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6358,10 +6362,10 @@
         <v>75</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>75</v>
@@ -6369,10 +6373,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6395,16 +6399,16 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6454,7 +6458,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6472,7 +6476,7 @@
         <v>75</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>75</v>
@@ -6483,14 +6487,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6509,16 +6513,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6568,7 +6572,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6586,7 +6590,7 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>75</v>
@@ -6597,10 +6601,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6623,19 +6627,19 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -6684,7 +6688,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6702,7 +6706,7 @@
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>75</v>
@@ -6713,10 +6717,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6739,16 +6743,16 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6777,10 +6781,10 @@
         <v>143</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6798,7 +6802,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6816,7 +6820,7 @@
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>75</v>
@@ -6827,10 +6831,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6853,16 +6857,16 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6912,7 +6916,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6930,25 +6934,25 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6967,19 +6971,19 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -7028,7 +7032,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7046,21 +7050,21 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7083,16 +7087,16 @@
         <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7142,7 +7146,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7171,10 +7175,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7197,16 +7201,16 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7256,7 +7260,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7285,10 +7289,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7314,13 +7318,13 @@
         <v>167</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7349,10 +7353,10 @@
         <v>151</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -7370,7 +7374,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7399,14 +7403,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7425,16 +7429,16 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7484,7 +7488,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7513,10 +7517,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7539,16 +7543,16 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7598,7 +7602,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7627,10 +7631,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7656,10 +7660,10 @@
         <v>167</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7689,10 +7693,10 @@
         <v>151</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -7710,7 +7714,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7739,10 +7743,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7765,16 +7769,16 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7824,7 +7828,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7853,10 +7857,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7879,16 +7883,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7938,7 +7942,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7967,10 +7971,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7993,16 +7997,16 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8052,7 +8056,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8081,10 +8085,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8193,10 +8197,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8307,14 +8311,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8336,10 +8340,10 @@
         <v>106</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>109</v>
@@ -8394,7 +8398,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8423,10 +8427,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8452,10 +8456,10 @@
         <v>167</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8506,7 +8510,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8535,10 +8539,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8564,10 +8568,10 @@
         <v>99</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8618,7 +8622,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8647,10 +8651,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8676,10 +8680,10 @@
         <v>167</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8709,10 +8713,10 @@
         <v>151</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -8730,7 +8734,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8759,10 +8763,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8788,10 +8792,10 @@
         <v>99</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8842,7 +8846,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8871,10 +8875,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8897,13 +8901,13 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8954,7 +8958,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8983,10 +8987,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9095,10 +9099,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9209,14 +9213,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9238,10 +9242,10 @@
         <v>106</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>109</v>
@@ -9296,7 +9300,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9325,10 +9329,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9354,10 +9358,10 @@
         <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9408,7 +9412,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -9437,10 +9441,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9466,10 +9470,10 @@
         <v>127</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9520,7 +9524,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9549,10 +9553,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9578,10 +9582,10 @@
         <v>99</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9632,7 +9636,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9661,10 +9665,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9690,10 +9694,10 @@
         <v>167</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9723,10 +9727,10 @@
         <v>151</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>75</v>
@@ -9744,7 +9748,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9773,10 +9777,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9799,16 +9803,16 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9858,7 +9862,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -9887,10 +9891,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9999,10 +10003,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10113,14 +10117,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10142,10 +10146,10 @@
         <v>106</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>109</v>
@@ -10200,7 +10204,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10229,10 +10233,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10258,10 +10262,10 @@
         <v>167</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10312,7 +10316,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10341,10 +10345,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10370,10 +10374,10 @@
         <v>99</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10424,7 +10428,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10453,10 +10457,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10482,10 +10486,10 @@
         <v>99</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10536,7 +10540,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -10565,10 +10569,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10591,19 +10595,19 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>75</v>
@@ -10652,7 +10656,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -10681,10 +10685,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10793,10 +10797,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10907,14 +10911,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -10936,10 +10940,10 @@
         <v>106</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>109</v>
@@ -10994,7 +10998,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11023,10 +11027,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11052,13 +11056,13 @@
         <v>167</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11108,7 +11112,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11137,10 +11141,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11166,13 +11170,13 @@
         <v>139</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11201,10 +11205,10 @@
         <v>143</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>75</v>
@@ -11222,7 +11226,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11251,10 +11255,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11280,10 +11284,10 @@
         <v>99</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11334,7 +11338,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11363,10 +11367,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11389,13 +11393,13 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11446,7 +11450,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -11475,10 +11479,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11587,10 +11591,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11701,14 +11705,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -11730,10 +11734,10 @@
         <v>106</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>109</v>
@@ -11788,7 +11792,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -11817,10 +11821,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11846,10 +11850,10 @@
         <v>167</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11900,7 +11904,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -11929,10 +11933,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11955,13 +11959,13 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12012,7 +12016,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12041,10 +12045,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12070,10 +12074,10 @@
         <v>77</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12124,7 +12128,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>

--- a/ig/improve-doc/StructureDefinition-ans-shareable-codesystem.xlsx
+++ b/ig/improve-doc/StructureDefinition-ans-shareable-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-02T16:50:25+00:00</t>
+    <t>2024-12-04T07:44:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
